--- a/student-submissions/timelog.xlsx
+++ b/student-submissions/timelog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52640ecffeb77e34/Desktop/ap-csp_25-26/student-submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0496242-5FD5-44C8-B07D-54C92EAA1DDF}"/>
+  <xr:revisionPtr revIDLastSave="432" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7382546C-3962-4B59-86FC-7B2A9869C47D}"/>
   <bookViews>
     <workbookView xWindow="5595" yWindow="3870" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -365,8 +365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:G50" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:G51" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D7DFE132-8D06-4200-B59C-2AA5013F5117}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{4BBA18C6-2B58-4ABE-848F-D6FEBC7AB0AF}" name="Topics"/>
@@ -643,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1630,6 +1630,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>49739</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/student-submissions/timelog.xlsx
+++ b/student-submissions/timelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52640ecffeb77e34/Desktop/ap-csp_25-26/student-submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7382546C-3962-4B59-86FC-7B2A9869C47D}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195CE62E-7134-40F6-9A70-60897ED2B5C6}"/>
   <bookViews>
     <workbookView xWindow="5595" yWindow="3870" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -252,6 +252,18 @@
   </si>
   <si>
     <t>Library link: 5743df90-4636-4e2a-becb-65433b8d8ba4</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>12:50pm</t>
+  </si>
+  <si>
+    <t>3:10pm</t>
+  </si>
+  <si>
+    <t>4:45pm</t>
   </si>
 </sst>
 </file>
@@ -365,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:G51" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G55" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:G55" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D7DFE132-8D06-4200-B59C-2AA5013F5117}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{4BBA18C6-2B58-4ABE-848F-D6FEBC7AB0AF}" name="Topics"/>
@@ -643,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1650,6 +1662,80 @@
         <v>15</v>
       </c>
     </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B55" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/student-submissions/timelog.xlsx
+++ b/student-submissions/timelog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52640ecffeb77e34/Desktop/ap-csp_25-26/student-submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195CE62E-7134-40F6-9A70-60897ED2B5C6}"/>
+  <xr:revisionPtr revIDLastSave="471" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE4A09B-5184-4635-92CE-929855CEA975}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="3870" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>4:45pm</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>4:25pm</t>
+  </si>
+  <si>
+    <t>5:20pm</t>
   </si>
 </sst>
 </file>
@@ -377,8 +386,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G55" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:G55" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G58" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:G58" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D7DFE132-8D06-4200-B59C-2AA5013F5117}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{4BBA18C6-2B58-4ABE-848F-D6FEBC7AB0AF}" name="Topics"/>
@@ -655,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1736,6 +1745,60 @@
         <v>1</v>
       </c>
     </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E58">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/student-submissions/timelog.xlsx
+++ b/student-submissions/timelog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52640ecffeb77e34/Desktop/ap-csp_25-26/student-submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="471" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE4A09B-5184-4635-92CE-929855CEA975}"/>
+  <xr:revisionPtr revIDLastSave="511" documentId="11_F25DC773A252ABDACC104851519951F65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{724EBA44-EF8F-4309-B224-B3013A00C01C}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -273,6 +273,36 @@
   </si>
   <si>
     <t>5:20pm</t>
+  </si>
+  <si>
+    <t>11am</t>
+  </si>
+  <si>
+    <t>diagnostic test</t>
+  </si>
+  <si>
+    <t>Practice test 1</t>
+  </si>
+  <si>
+    <t>Practice test 2</t>
+  </si>
+  <si>
+    <t>4:00pm</t>
+  </si>
+  <si>
+    <t>videos</t>
+  </si>
+  <si>
+    <t>9:00pm</t>
+  </si>
+  <si>
+    <t>10:00pm</t>
+  </si>
+  <si>
+    <t>8:45pm</t>
+  </si>
+  <si>
+    <t>9:55pm</t>
   </si>
 </sst>
 </file>
@@ -386,8 +416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G58" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:G58" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}" name="Table1" displayName="Table1" ref="A1:G64" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:G64" xr:uid="{AE583CA1-19F4-4655-8238-5B4F7D02D2E6}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D7DFE132-8D06-4200-B59C-2AA5013F5117}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{4BBA18C6-2B58-4ABE-848F-D6FEBC7AB0AF}" name="Topics"/>
@@ -664,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1799,6 +1829,123 @@
         <v>10</v>
       </c>
     </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>46121</v>
+      </c>
+      <c r="B60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
+        <v>59</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B63" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
